--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ra91777a10acb4470"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2730d25cf2d442b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R8be45b55854a4e22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R09651ceab7a14398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R0f8e32d2311f49ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rc2965a8a032b4d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R3bd01e7992ba45c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3458fd9bb84042d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re5faba8a9869473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6c56c3e025fd4b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R8023c75139354f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rd081bea84c3c4f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R45fe37441db04e27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rab0169babc464c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rd1266af8de244035"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rf0569943dc0c4580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R8bb06c421b814307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7674d4fc1a964742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Ra69796d4a63e4f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R26c31c7ed28746d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R14401755d7904ede"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R3eea441bfb8448d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R973d6f1aa59d4bbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Ra9da02d820464b10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R755b01b054854404"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf597461da49f423a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R0a1904d0eb444c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R280955af45c146c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R41d6bcb8074a4e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2249c809d13147e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Re550c7ce9ee340d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rbcfd29c1d7034adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rec7936b3fdde4993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rf3dd61a2485046ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R1c38c15848924318"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R84a56de036ae4654"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R9ea20d461d054ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rbee612e235fc43ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R828cae6165964f79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R08ed4537ef524a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rcc2181aaf5c7466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Re23d36487bdb42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R5da95c08414442ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rc584b60c6b364010"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rf52b8495fb834f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2bed61a46fc0464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R751295d230d14a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rd3d01c728563452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra09447224e0744dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rc5ed67e4da604145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R93bacb91af8c4edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R733259b362a84620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R870d289e87ff4401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R47ae55f88b4f4db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R73816a82ad664fe6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R494e60e1e33e40b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2285,11 +2285,11 @@
       </x:c>
       <x:c r="C10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$14,"Défini")</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$14,"Prototype")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$14,"Intégré")</x:f>
@@ -3678,11 +3678,11 @@
       </x:c>
       <x:c r="C37" s="41" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D37" s="41" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="41" t="n">
         <x:f>SUM(E10:E35)</x:f>
@@ -4285,7 +4285,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7910e8db774183"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a7a62f1b5a9432b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4974,7 +4974,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R972a6766af1b4ba6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0f2cdd67bfc48c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5663,7 +5663,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R426ed0d04eb14f97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2f0549c0b6547c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6352,7 +6352,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R411eeef4fa784f38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R237529fba5194102"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7377,7 +7377,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6337ab360af34f6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2574e38711c489c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8066,7 +8066,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R976421fac00142ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434991f3618748b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8394,7 +8394,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R170e26179d3d4af5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11ee8af7e8764ebf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8722,7 +8722,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80f2cee1101041f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R450139a44c544efa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9050,7 +9050,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96f0004e5c74b68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf6a2014b6b74582"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9623,7 +9623,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50530064d6fa40e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec4429eb00554696"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9650,7 +9650,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="78" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="233" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -9829,7 +9829,7 @@
         <x:v>James Vega</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -9848,7 +9848,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Réserver actor.pl.vega ; rôle de référence : équipier.</x:v>
+        <x:v>Prototype Chroniques : src/universe-actors.js, src/chronicles.js. Identifiant runtime PL-CHR-VEGA ; contexte d’œuvre/segment et sélection de scène obligatoires.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Paragon Lost est un film, pas une série. Préserver les pertes et la décision finale de Vega ; les choix jouables portent sur les méthodes locales. Toute variante contrefactuelle éventuelle doit être séparée du module de continuité, et n’est pas définie ici.</x:v>
@@ -9867,7 +9867,7 @@
         <x:v>https://blog.bioware.com/2013/03/12/mass-effect-paragon-lost-available-now-in-the-uk/</x:v>
       </x:c>
       <x:c r="S7" s="20" t="str">
-        <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
+        <x:v>Contrôler le modèle contre le film avant dessin définitif. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
@@ -10245,7 +10245,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fe51a79f38942f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe535d34fbb44390"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10730,7 +10730,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65fb05fa96e4e62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4987285896e64f8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11725,7 +11725,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R505891024f004102"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b9eafa7723f4290"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12720,7 +12720,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R526d1e0481e540ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48b46af23fed44c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13205,7 +13205,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96c785775a014637"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R604ccaf3230749e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13729,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb88484c004d4184"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde28d73a270747e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14400,7 +14400,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8119bdbe4c11400e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R800cd82c1bac42b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15261,7 +15261,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40a0fdbb27c04a29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12510b2d41544fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15969,7 +15969,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7841bec987454318"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4298081729034798"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16081,12 +16081,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="54" customHeight="1">
+    <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Delta Squad, Fehl Prime, Treeya et attaque des Récolteurs ; fiches de production originales couvrant coopération tactique, protection civile et conséquences du commandement.</x:v>
+        <x:v>Delta Squad, Fehl Prime, Treeya et attaque des Récolteurs ; fiches de production originales couvrant coopération tactique, protection civile et conséquences du commandement. Prototype partiel : 1 profils sélectionnables et 0 équipements en Chroniques ; le reste demeure documentaire.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -16105,7 +16105,7 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
@@ -16649,10 +16649,16 @@
       <x:c r="E48" s="2"/>
       <x:c r="F48" s="2"/>
     </x:row>
-    <x:row r="49" ht="22" customHeight="1">
-      <x:c r="A49" s="2"/>
-      <x:c r="B49" s="2"/>
-      <x:c r="C49" s="2"/>
+    <x:row r="49" ht="96" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>Prototype Chroniques indépendant</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>1 personnages sélectionnables, 0 équipements utilisables sous restrictions d’œuvre, segment, scène et porteur ; preuves dans implementationPaths et evidence des seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="str">
+        <x:v>Campagne complète, dialogues, acquisition canonique, sprites, costumes, animations et statistiques originales à réaliser ou vérifier. Les ateliers sont des essais de préparation ATB, sans progression canonique ni transfert ME1.</x:v>
+      </x:c>
       <x:c r="D49" s="2"/>
       <x:c r="E49" s="2"/>
       <x:c r="F49" s="2"/>
@@ -17208,6 +17214,14 @@
       <x:c r="D118" s="2"/>
       <x:c r="E118" s="2"/>
       <x:c r="F118" s="2"/>
+    </x:row>
+    <x:row r="119" ht="22" customHeight="1">
+      <x:c r="A119" s="2"/>
+      <x:c r="B119" s="2"/>
+      <x:c r="C119" s="2"/>
+      <x:c r="D119" s="2"/>
+      <x:c r="E119" s="2"/>
+      <x:c r="F119" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17782,7 +17796,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e7c5830ca2841cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36194398e6b84d3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18208,7 +18222,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc674cc8e071f4c12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca4f4898e0347b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18536,7 +18550,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb7045b736624eb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8efd6d35d84847af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19225,7 +19239,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R768bfaeaa6d84fa3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc26b8ebc3c61465d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19932,7 +19946,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5acd1ab9dbe44aff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R644cff1b3c994f4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20621,7 +20635,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b168d140d55467b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11994f51c2e4a72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21047,7 +21061,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a303ad636bf49dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51406e08d47c48a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R41d6bcb8074a4e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2249c809d13147e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Re550c7ce9ee340d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rbcfd29c1d7034adb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rec7936b3fdde4993"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rf3dd61a2485046ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R1c38c15848924318"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R84a56de036ae4654"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R9ea20d461d054ca6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rbee612e235fc43ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R828cae6165964f79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R08ed4537ef524a3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rcc2181aaf5c7466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Re23d36487bdb42de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R5da95c08414442ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rc584b60c6b364010"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rf52b8495fb834f0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2bed61a46fc0464f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R751295d230d14a78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rd3d01c728563452e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra09447224e0744dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rc5ed67e4da604145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R93bacb91af8c4edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R733259b362a84620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R870d289e87ff4401"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R47ae55f88b4f4db7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R73816a82ad664fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R494e60e1e33e40b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1f9ad7c058d34d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R232da891d9b541cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R46e19f86a34a42e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf0425610bebc4c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R7a05f51ba87b4b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Re7b6672a31ed40c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Ra5530181184f40ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R86798c1c45274f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R12b8c7fce3394624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf028406ffd9a49a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra7e7807a3c8e484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Ra0b87656ceac44dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R91b621d41e714e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rd60607ddc27545d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rf06278b41a4b4822"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R18f22433254148d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7bd896b37cce4876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R0414c86cddbb44ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R21cdcba184e54894"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rd54bd414a5994460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R8e20615534bb4d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rb0dba706f4584ea2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R575e334d709e4852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rcc8c5787c60b4f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R603bbbfd60004ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rbbc769a66c624cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R9349460597f04ee6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R07026d8506de435f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>199</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>160</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$14,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$14,"Établi")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$15,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$15,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$15,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$15,"P0")</x:f>
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$15,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$15,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$21)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$21,"Défini")</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$21,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$21,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$21,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$21,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$21,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$21,"Extrapolation")</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$21,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$21,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$21,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$21,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$15,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$21)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$21,"Défini")</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$21,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$21,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$21,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$21,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$21,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$21,"Extrapolation")</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$21,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$21,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$21,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$21,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$21)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$21,"Défini")</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$21,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$21,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$21,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$21,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$21,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$21,"Extrapolation")</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$21,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$21,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$21,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$21,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$15,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$19,"Défini")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$19,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$19,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$19,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$16,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$16,"P0")</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>199</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D37" s="41" t="n">
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E37" s="41" t="n">
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>160</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>24</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4044,8 +4038,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4095,8 +4089,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4146,8 +4140,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4197,8 +4191,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4248,8 +4242,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4285,7 +4279,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a7a62f1b5a9432b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1b62459b6874cad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4425,61 +4419,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4531,8 +4525,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4582,8 +4576,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4633,8 +4627,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4684,8 +4678,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4735,8 +4729,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4786,8 +4780,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4837,8 +4831,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4888,8 +4882,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -4939,8 +4933,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -4974,7 +4968,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0f2cdd67bfc48c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb86e2b25474469b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5114,61 +5108,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5220,8 +5214,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5271,8 +5265,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5322,8 +5316,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5373,8 +5367,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5424,8 +5418,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5475,8 +5469,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5526,8 +5520,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5577,8 +5571,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -5628,8 +5622,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -5663,7 +5657,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2f0549c0b6547c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R407239accaf14e08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5803,61 +5797,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5909,8 +5903,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5960,8 +5954,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6011,8 +6005,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6062,8 +6056,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6113,8 +6107,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6164,8 +6158,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6215,8 +6209,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6266,8 +6260,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -6317,8 +6311,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -6352,7 +6346,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R237529fba5194102"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2552fa891a694d15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6492,61 +6486,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6598,8 +6592,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6651,8 +6645,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6704,8 +6698,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6757,8 +6751,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6810,8 +6804,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6863,8 +6857,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6916,8 +6910,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6969,8 +6963,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7022,8 +7016,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7075,8 +7069,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7128,8 +7122,8 @@
       </x:c>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str">
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7181,8 +7175,8 @@
       </x:c>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str">
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7234,8 +7228,8 @@
       </x:c>
       <x:c r="P19" s="9" t="str"/>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str">
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7287,8 +7281,8 @@
       </x:c>
       <x:c r="P20" s="7" t="str"/>
       <x:c r="Q20" s="7" t="str"/>
-      <x:c r="R20" s="21" t="str"/>
-      <x:c r="S20" s="21" t="str">
+      <x:c r="R20" s="7" t="str"/>
+      <x:c r="S20" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7340,8 +7334,8 @@
       </x:c>
       <x:c r="P21" s="9" t="str"/>
       <x:c r="Q21" s="9" t="str"/>
-      <x:c r="R21" s="20" t="str"/>
-      <x:c r="S21" s="20" t="str">
+      <x:c r="R21" s="9" t="str"/>
+      <x:c r="S21" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -7377,7 +7371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2574e38711c489c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd44f6d0d7e45a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7517,61 +7511,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7623,8 +7617,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7674,8 +7668,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7725,8 +7719,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7776,8 +7770,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7827,8 +7821,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7878,8 +7872,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7929,8 +7923,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7980,8 +7974,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -8031,8 +8025,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -8066,7 +8060,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434991f3618748b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaeb2a80311842b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8206,61 +8200,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8306,10 +8300,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8355,10 +8349,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8394,7 +8388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11ee8af7e8764ebf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca1b5af85834712"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8534,61 +8528,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8634,10 +8628,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-MAKO</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/M35_Mako</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8683,10 +8677,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-BROOD</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Brood</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8722,7 +8716,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R450139a44c544efa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbee2165fb0114614"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8862,61 +8856,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8962,10 +8956,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-NICKY</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nicky</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -9011,10 +9005,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -9050,7 +9044,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf6a2014b6b74582"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1355b632f6d45c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9190,61 +9184,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9294,8 +9288,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9343,8 +9337,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9392,8 +9386,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9441,8 +9435,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9490,8 +9484,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9539,8 +9533,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -9588,8 +9582,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -9623,7 +9617,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec4429eb00554696"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5071daa88be41d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9763,61 +9757,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9863,10 +9857,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-BW</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://blog.bioware.com/2013/03/12/mass-effect-paragon-lost-available-now-in-the-uk/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
@@ -9912,10 +9906,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-TREEYA</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Treeya_Nuwani</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -9961,10 +9955,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -10010,10 +10004,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -10059,10 +10053,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>PL-SRC-NICKY</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nicky</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -10108,10 +10102,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -10157,10 +10151,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -10206,10 +10200,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>PL-SRC-BROOD</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Brood</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -10245,7 +10239,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe535d34fbb44390"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfd2b82fb78e405a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10385,61 +10379,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10491,8 +10485,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10542,8 +10536,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10593,8 +10587,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10644,8 +10638,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10695,8 +10689,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -10730,7 +10724,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4987285896e64f8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13c173abcfab4528"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10870,61 +10864,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10976,8 +10970,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11027,8 +11021,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11078,8 +11072,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11129,8 +11123,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11180,8 +11174,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11231,8 +11225,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11282,8 +11276,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11333,8 +11327,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11384,8 +11378,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11435,8 +11429,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -11486,8 +11480,8 @@
       </x:c>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -11537,8 +11531,8 @@
       </x:c>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -11588,8 +11582,8 @@
       </x:c>
       <x:c r="P19" s="9" t="str"/>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="19" t="str">
@@ -11639,8 +11633,8 @@
       </x:c>
       <x:c r="P20" s="7" t="str"/>
       <x:c r="Q20" s="7" t="str"/>
-      <x:c r="R20" s="21" t="str"/>
-      <x:c r="S20" s="21" t="str"/>
+      <x:c r="R20" s="7" t="str"/>
+      <x:c r="S20" s="7" t="str"/>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="18" t="str">
@@ -11690,8 +11684,8 @@
       </x:c>
       <x:c r="P21" s="9" t="str"/>
       <x:c r="Q21" s="9" t="str"/>
-      <x:c r="R21" s="20" t="str"/>
-      <x:c r="S21" s="20" t="str"/>
+      <x:c r="R21" s="9" t="str"/>
+      <x:c r="S21" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D21">
@@ -11725,7 +11719,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b9eafa7723f4290"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re681b14a869e4371"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11865,61 +11859,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11971,8 +11965,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12022,8 +12016,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12073,8 +12067,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12124,8 +12118,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12175,8 +12169,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12226,8 +12220,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12277,8 +12271,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12328,8 +12322,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -12379,8 +12373,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -12430,8 +12424,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -12481,8 +12475,8 @@
       </x:c>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -12532,8 +12526,8 @@
       </x:c>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -12583,8 +12577,8 @@
       </x:c>
       <x:c r="P19" s="9" t="str"/>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
     <x:row r="20" ht="68" customHeight="1">
       <x:c r="A20" s="19" t="str">
@@ -12634,8 +12628,8 @@
       </x:c>
       <x:c r="P20" s="7" t="str"/>
       <x:c r="Q20" s="7" t="str"/>
-      <x:c r="R20" s="21" t="str"/>
-      <x:c r="S20" s="21" t="str"/>
+      <x:c r="R20" s="7" t="str"/>
+      <x:c r="S20" s="7" t="str"/>
     </x:row>
     <x:row r="21" ht="68" customHeight="1">
       <x:c r="A21" s="18" t="str">
@@ -12685,8 +12679,8 @@
       </x:c>
       <x:c r="P21" s="9" t="str"/>
       <x:c r="Q21" s="9" t="str"/>
-      <x:c r="R21" s="20" t="str"/>
-      <x:c r="S21" s="20" t="str"/>
+      <x:c r="R21" s="9" t="str"/>
+      <x:c r="S21" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D21">
@@ -12720,7 +12714,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48b46af23fed44c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0df455e351f34224"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12860,61 +12854,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12966,8 +12960,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13017,8 +13011,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13068,8 +13062,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13119,8 +13113,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13170,8 +13164,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -13205,7 +13199,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R604ccaf3230749e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02236d19ee624ecb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13345,61 +13339,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13449,8 +13443,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13498,8 +13492,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13547,8 +13541,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13596,8 +13590,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13645,8 +13639,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13694,8 +13688,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -13729,7 +13723,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde28d73a270747e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34d2b6a1497e413f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13869,61 +13863,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13973,8 +13967,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14022,8 +14016,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -14071,8 +14065,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -14120,8 +14114,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -14169,8 +14163,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -14218,8 +14212,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -14267,8 +14261,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -14316,8 +14310,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -14365,8 +14359,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -14400,7 +14394,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R800cd82c1bac42b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R512acfb4069e4387"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14540,61 +14534,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14646,8 +14640,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14697,8 +14691,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -14748,8 +14742,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -14799,8 +14793,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -14850,8 +14844,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -14901,8 +14895,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -14952,8 +14946,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -15003,8 +14997,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -15054,8 +15048,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -15097,8 +15091,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="82" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -15140,8 +15134,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -15183,8 +15177,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -15226,8 +15220,8 @@
       <x:c r="O19" s="9" t="str"/>
       <x:c r="P19" s="9" t="str"/>
       <x:c r="Q19" s="9" t="str"/>
-      <x:c r="R19" s="20" t="str"/>
-      <x:c r="S19" s="20" t="str"/>
+      <x:c r="R19" s="9" t="str"/>
+      <x:c r="S19" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D19">
@@ -15261,7 +15255,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12510b2d41544fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e11f882d31f4210"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15401,61 +15395,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15501,10 +15495,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-BW</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://blog.bioware.com/2013/03/12/mass-effect-paragon-lost-available-now-in-the-uk/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15550,10 +15544,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15599,10 +15593,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15648,10 +15642,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>PL-SRC-FEHL</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Fehl_Prime</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15697,10 +15691,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>PL-SRC-BROOD</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Brood</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15746,10 +15740,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15795,10 +15789,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>PL-SRC-CERB</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Cerberus</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15842,8 +15836,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15887,8 +15881,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15932,8 +15926,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -15969,7 +15963,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4298081729034798"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e87a48f35b44c4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16034,10 +16028,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -16109,7 +16103,7 @@
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -16262,22 +16256,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -16566,13 +16560,13 @@
       <x:c r="F42" s="2"/>
     </x:row>
     <x:row r="43" ht="34" customHeight="1">
-      <x:c r="A43" s="30" t="str">
+      <x:c r="A43" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B43" s="31" t="str">
+      <x:c r="B43" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C43" s="32" t="str">
+      <x:c r="C43" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D43" s="2"/>
@@ -17363,61 +17357,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17463,10 +17457,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-DELTA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Delta_Squad</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -17512,10 +17506,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-MESSNER</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Messner</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -17561,10 +17555,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -17610,10 +17604,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -17659,10 +17653,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -17708,10 +17702,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -17757,10 +17751,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>PL-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Paragon_Lost</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Contrôler le modèle contre le film avant dessin définitif.</x:v>
       </x:c>
     </x:row>
@@ -17796,7 +17790,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36194398e6b84d3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2507588fecd4099"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17936,61 +17930,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18036,10 +18030,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-DELTA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Delta_Squad</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18085,10 +18079,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-BROOD</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Brood</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18134,10 +18128,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>PL-SRC-FEHL</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Fehl_Prime</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18183,10 +18177,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>PL-SRC-MESSNER</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Messner</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18222,7 +18216,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca4f4898e0347b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b3ca1c21ebe414e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18362,61 +18356,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18462,10 +18456,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-FEHL</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Fehl_Prime</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18511,10 +18505,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-TREEYA</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Treeya_Nuwani</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18550,7 +18544,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8efd6d35d84847af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cd4af43643e4ece"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18690,61 +18684,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18794,8 +18788,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -18845,8 +18839,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -18896,8 +18890,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -18947,8 +18941,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -18998,8 +18992,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -19049,8 +19043,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -19100,8 +19094,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -19151,8 +19145,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -19202,8 +19196,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -19239,7 +19233,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc26b8ebc3c61465d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra188c69257ca4a25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19379,61 +19373,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -19485,8 +19479,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19538,8 +19532,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19591,8 +19585,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19644,8 +19638,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19697,8 +19691,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19750,8 +19744,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19803,8 +19797,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19856,8 +19850,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19909,8 +19903,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -19946,7 +19940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R644cff1b3c994f4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdebac86845b74054"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20086,61 +20080,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -20192,8 +20186,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -20243,8 +20237,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -20294,8 +20288,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -20345,8 +20339,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -20396,8 +20390,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -20447,8 +20441,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -20498,8 +20492,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -20549,8 +20543,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -20600,8 +20594,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -20635,7 +20629,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11994f51c2e4a72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c425441948d4408"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20775,61 +20769,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -20875,10 +20869,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>PL-SRC-BROOD</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Brood</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -20924,10 +20918,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>PL-SRC-MESSNER</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Messner</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -20973,10 +20967,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>PL-SRC-MESSNER</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Messner</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -21022,10 +21016,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>PL-SRC-MILQUE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Milque</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -21061,7 +21055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51406e08d47c48a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779007e8af5c4057"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1f9ad7c058d34d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R232da891d9b541cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R46e19f86a34a42e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf0425610bebc4c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R7a05f51ba87b4b1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Re7b6672a31ed40c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Ra5530181184f40ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R86798c1c45274f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R12b8c7fce3394624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf028406ffd9a49a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra7e7807a3c8e484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Ra0b87656ceac44dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R91b621d41e714e3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rd60607ddc27545d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rf06278b41a4b4822"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R18f22433254148d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7bd896b37cce4876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R0414c86cddbb44ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R21cdcba184e54894"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rd54bd414a5994460"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R8e20615534bb4d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rb0dba706f4584ea2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R575e334d709e4852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rcc8c5787c60b4f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R603bbbfd60004ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rbbc769a66c624cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R9349460597f04ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R07026d8506de435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Raedfcd591ef84806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R669ffe7b83664b7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rc4f0779c09404fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf43966fd56414b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Ra7fb83c6d29b4fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Ra0e71f407df24ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R09ed8ccc5e9948d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R9820b8a88ab6414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rb76825a887d94ce8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R9faf8b240e644a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra010205317dc443c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R97a703a37e4f4aa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rcda082f5c52b4410"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R3a67e99f415a49c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R343a05057ae44002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re22b320a501a4ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rfd0f0e43eeb446a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rb8a7d52dcae54d9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rf3d3167a26d74fcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rbb28f5226a7d4220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rbac3211fb00a4ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R65e192c8b3f8438c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rf42b208a02404920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbd72da9080f74107"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1ed7047058ee475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R92a7d795a0504329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rcbafd0d7695542ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rba8e7721d55747a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4279,7 +4279,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1b62459b6874cad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4a9c0e04ddf41c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4968,7 +4968,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb86e2b25474469b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70d27b32200f4c35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5657,7 +5657,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R407239accaf14e08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77d11357ef9c457c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6346,7 +6346,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2552fa891a694d15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ecb46f230f04c91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7371,7 +7371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd44f6d0d7e45a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a988301d27446d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8060,7 +8060,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaeb2a80311842b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28e0cb1f99de4eb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8388,7 +8388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca1b5af85834712"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb83bf639c1d4693"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8716,7 +8716,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbee2165fb0114614"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ab8a39c5954e65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9044,7 +9044,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1355b632f6d45c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3c15b2c659441ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9617,7 +9617,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5071daa88be41d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb259fe5d79be4d0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10239,7 +10239,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfd2b82fb78e405a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf2acd95e7784189"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10724,7 +10724,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13c173abcfab4528"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2aee67a713ba4617"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11719,7 +11719,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re681b14a869e4371"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a9ca831d71410c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12714,7 +12714,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0df455e351f34224"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd7c453fb5be4272"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13199,7 +13199,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02236d19ee624ecb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfdd9bee726f41f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13723,7 +13723,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34d2b6a1497e413f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fdae15afc894499"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14394,7 +14394,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R512acfb4069e4387"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfef6a877cddd4015"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15255,7 +15255,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e11f882d31f4210"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa5a24e049ca4a0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15963,7 +15963,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e87a48f35b44c4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a93388e5767440c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17790,7 +17790,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2507588fecd4099"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37481456220c4126"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18216,7 +18216,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b3ca1c21ebe414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c07166c47c24d7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18544,7 +18544,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cd4af43643e4ece"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465ab8d6b2da4350"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19233,7 +19233,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra188c69257ca4a25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c63dd5666e44f39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19940,7 +19940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdebac86845b74054"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd19eec2de6b47ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20629,7 +20629,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c425441948d4408"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34ab4274c84c432a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21055,7 +21055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779007e8af5c4057"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re44e8b89aac34187"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Paragon_Lost_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Raedfcd591ef84806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R669ffe7b83664b7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rc4f0779c09404fa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf43966fd56414b6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Ra7fb83c6d29b4fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Ra0e71f407df24ea6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R09ed8ccc5e9948d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R9820b8a88ab6414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rb76825a887d94ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R9faf8b240e644a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra010205317dc443c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R97a703a37e4f4aa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rcda082f5c52b4410"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R3a67e99f415a49c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R343a05057ae44002"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re22b320a501a4ddb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rfd0f0e43eeb446a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rb8a7d52dcae54d9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rf3d3167a26d74fcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rbb28f5226a7d4220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rbac3211fb00a4ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R65e192c8b3f8438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rf42b208a02404920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbd72da9080f74107"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1ed7047058ee475c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R92a7d795a0504329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rcbafd0d7695542ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rba8e7721d55747a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0677c5c0eeeb43a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2065af8e7dcf43cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R5d49b22deac94a94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf3f14598e292422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R3f476372c7a44e6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3d9d7637e3434bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R18fafac770da457b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R14f1d0fdbee24cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R49fa5f53a9324a4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rd26ff39892b14bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R95db670e1c8b4f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rd5dc11d394e14e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R9a6a8eb5fbbc45a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R46c7844dfa1342dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R5d04e72a6a304c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Raf8ce38a870843eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R2e33800f7e2943d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R1da074bad56c408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R6f30bca73acf4a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R5970e5e81ab44901"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rfdbbf37477e94f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Ra618ae3d3cae43a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rd0e659c3eb4742a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R38a0162ac28b4e03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rfc2cd7f94fa04b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R8598542e06bb4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Raa0be141fa584666"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rfcbafbf508b74896"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4279,7 +4279,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4a9c0e04ddf41c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20fced0bb7e94917"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4968,7 +4968,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70d27b32200f4c35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R299203704e834d13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5657,7 +5657,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77d11357ef9c457c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refb37e45bf3f4ea3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6346,7 +6346,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ecb46f230f04c91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ac9fdad33a41b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7371,7 +7371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a988301d27446d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1275dc14d89c4031"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8060,7 +8060,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28e0cb1f99de4eb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf847bd28eedf492c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8388,7 +8388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb83bf639c1d4693"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaf3312ac03340a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8716,7 +8716,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ab8a39c5954e65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2ea4ed467d74680"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9044,7 +9044,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3c15b2c659441ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbef8351e455843ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9617,7 +9617,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb259fe5d79be4d0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8455f40bc02c49b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10239,7 +10239,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf2acd95e7784189"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rceb73561519b4de1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10724,7 +10724,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2aee67a713ba4617"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60df95ef76944edb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11719,7 +11719,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a9ca831d71410c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaa64d6d79ec4f5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12714,7 +12714,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd7c453fb5be4272"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6988768349e84bd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13199,7 +13199,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfdd9bee726f41f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd327c60c60ad44e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13723,7 +13723,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fdae15afc894499"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44ae93d0d47048db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14394,7 +14394,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfef6a877cddd4015"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15d8f7ec2bf84dde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15255,7 +15255,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa5a24e049ca4a0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd68ff4bd2dd541f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15963,7 +15963,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a93388e5767440c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd48447b74304480"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17790,7 +17790,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37481456220c4126"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65f9f9db1a054937"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18216,7 +18216,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c07166c47c24d7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1f14205e7b147b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18544,7 +18544,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465ab8d6b2da4350"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d263d30d5a74613"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19233,7 +19233,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c63dd5666e44f39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95105c38ed0f46bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19940,7 +19940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd19eec2de6b47ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75c68382e3d54dff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20629,7 +20629,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34ab4274c84c432a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe04eaf71ede4e5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21055,7 +21055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re44e8b89aac34187"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27782462bb5048b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>